--- a/diseases/d127/2020-2025.xlsx
+++ b/diseases/d127/2020-2025.xlsx
@@ -5099,6 +5099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12187,6 +12192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12335,6 +12345,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12483,6 +12498,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12631,6 +12651,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12779,6 +12804,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12927,6 +12957,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13075,6 +13110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13223,6 +13263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13371,6 +13416,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13519,6 +13569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13667,6 +13722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17412,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24440,6 +24505,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24588,6 +24658,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24736,6 +24811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24884,6 +24964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25032,6 +25117,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25180,6 +25270,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25328,6 +25423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25476,6 +25576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25624,6 +25729,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25772,6 +25882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25920,6 +26035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30391,6 +30511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36837,6 +36962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36985,6 +37115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37133,6 +37268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37281,6 +37421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37429,6 +37574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37577,6 +37727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37725,6 +37880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37873,6 +38033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38021,6 +38186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38169,6 +38339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38317,6 +38492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42788,6 +42968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50030,6 +50215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50178,6 +50368,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50326,6 +50521,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50474,6 +50674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50622,6 +50827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50770,6 +50980,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50918,6 +51133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51066,6 +51286,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51214,6 +51439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51362,6 +51592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51510,6 +51745,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51658,6 +51898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51806,6 +52051,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51954,6 +52204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52102,6 +52357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52250,6 +52510,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52398,6 +52663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52546,6 +52816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52694,6 +52969,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52842,6 +53122,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52990,6 +53275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53138,6 +53428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53286,6 +53581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53434,6 +53734,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53582,6 +53887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53730,6 +54040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53878,6 +54193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54026,6 +54346,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54174,6 +54499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54322,6 +54652,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54470,6 +54805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54618,6 +54958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54766,6 +55111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54914,6 +55264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55060,6 +55415,11 @@
       <c r="S295" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">

--- a/diseases/d127/2020-2025.xlsx
+++ b/diseases/d127/2020-2025.xlsx
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         </is>
       </c>
       <c r="AT147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         </is>
       </c>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>

--- a/diseases/d127/2020-2025.xlsx
+++ b/diseases/d127/2020-2025.xlsx
@@ -5094,6 +5094,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5106,12 +5111,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -11779,6 +11794,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11791,12 +11811,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -11917,6 +11947,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11929,12 +11964,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -12055,6 +12100,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12067,12 +12117,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -12193,6 +12253,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12205,12 +12270,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -12331,6 +12406,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12343,12 +12423,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -12469,6 +12559,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12481,12 +12576,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -12607,6 +12712,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12619,12 +12729,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -12745,6 +12865,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12757,12 +12882,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -12883,6 +13018,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12895,12 +13035,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -13021,6 +13171,11 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13033,12 +13188,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -13159,6 +13324,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13171,12 +13341,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -16834,6 +17014,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16846,12 +17031,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -23519,6 +23714,11 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23531,12 +23731,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -23657,6 +23867,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23669,12 +23884,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -23795,6 +24020,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23807,12 +24037,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -23933,6 +24173,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23945,12 +24190,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -24071,6 +24326,11 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24083,12 +24343,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -24209,6 +24479,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24221,12 +24496,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -24347,6 +24632,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24359,12 +24649,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -24485,6 +24785,11 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24497,12 +24802,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -24623,6 +24938,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24635,12 +24955,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -24761,6 +25091,11 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24773,12 +25108,22 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -24899,6 +25244,11 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24911,12 +25261,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -29360,6 +29720,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29372,12 +29737,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -35403,6 +35778,11 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35415,12 +35795,22 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -35541,6 +35931,11 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35553,12 +35948,22 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -35679,6 +36084,11 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35691,12 +36101,22 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -35817,6 +36237,11 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35829,12 +36254,22 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -35955,6 +36390,11 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35967,12 +36407,22 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -36093,6 +36543,11 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36105,12 +36560,22 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -36231,6 +36696,11 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36243,12 +36713,22 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -36369,6 +36849,11 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36381,12 +36866,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -36507,6 +37002,11 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36519,12 +37019,22 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -36645,6 +37155,11 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36657,12 +37172,22 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -36783,6 +37308,11 @@
       <c r="R195" t="n">
         <v>0</v>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36795,12 +37325,22 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -41244,6 +41784,11 @@
       <c r="R218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41256,12 +41801,22 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -48083,6 +48638,11 @@
       <c r="R253" t="n">
         <v>0</v>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48095,12 +48655,22 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -48221,6 +48791,11 @@
       <c r="R254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48233,12 +48808,22 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -48359,6 +48944,11 @@
       <c r="R255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48371,12 +48961,22 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -48497,6 +49097,11 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48509,12 +49114,22 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -48635,6 +49250,11 @@
       <c r="R257" t="n">
         <v>0</v>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48647,12 +49267,22 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
         <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
@@ -48773,6 +49403,11 @@
       <c r="R258" t="n">
         <v>0</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48785,12 +49420,22 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -48911,6 +49556,11 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48923,12 +49573,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -49049,6 +49709,11 @@
       <c r="R260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49061,12 +49726,22 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
@@ -49187,6 +49862,11 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49199,12 +49879,22 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -49325,6 +50015,11 @@
       <c r="R262" t="n">
         <v>0</v>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49337,12 +50032,22 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
         <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
@@ -49463,6 +50168,11 @@
       <c r="R263" t="n">
         <v>0</v>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49475,12 +50185,22 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
         <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
@@ -49601,6 +50321,11 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49613,12 +50338,22 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
         <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -49739,6 +50474,11 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49751,12 +50491,22 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -49877,6 +50627,11 @@
       <c r="R266" t="n">
         <v>0</v>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49889,12 +50644,22 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
         <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
@@ -50015,6 +50780,11 @@
       <c r="R267" t="n">
         <v>0</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50027,12 +50797,22 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
@@ -50153,6 +50933,11 @@
       <c r="R268" t="n">
         <v>0</v>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50165,12 +50950,22 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
         <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
@@ -50291,6 +51086,11 @@
       <c r="R269" t="n">
         <v>0</v>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50303,12 +51103,22 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
         <v>0</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
@@ -50429,6 +51239,11 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50441,12 +51256,22 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -50567,6 +51392,11 @@
       <c r="R271" t="n">
         <v>0</v>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50579,12 +51409,22 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
         <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
@@ -50705,6 +51545,11 @@
       <c r="R272" t="n">
         <v>0</v>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50717,12 +51562,22 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
         <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
@@ -50843,6 +51698,11 @@
       <c r="R273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50855,12 +51715,22 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
@@ -50981,6 +51851,11 @@
       <c r="R274" t="n">
         <v>0</v>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50993,12 +51868,22 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
         <v>0</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
@@ -51119,6 +52004,11 @@
       <c r="R275" t="n">
         <v>0</v>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51131,12 +52021,22 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
         <v>0</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
@@ -51257,6 +52157,11 @@
       <c r="R276" t="n">
         <v>0</v>
       </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51269,12 +52174,22 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS276" t="inlineStr"/>
       <c r="AT276" t="n">
         <v>0</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
@@ -51395,6 +52310,11 @@
       <c r="R277" t="n">
         <v>0</v>
       </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51407,12 +52327,22 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
         <v>0</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
@@ -51533,6 +52463,11 @@
       <c r="R278" t="n">
         <v>0</v>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51545,12 +52480,22 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
         <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
@@ -51671,6 +52616,11 @@
       <c r="R279" t="n">
         <v>0</v>
       </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA279" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51683,12 +52633,22 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
         <v>0</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
@@ -51809,6 +52769,11 @@
       <c r="R280" t="n">
         <v>0</v>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51821,12 +52786,22 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
@@ -51947,6 +52922,11 @@
       <c r="R281" t="n">
         <v>0</v>
       </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51959,12 +52939,22 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
@@ -52085,6 +53075,11 @@
       <c r="R282" t="n">
         <v>0</v>
       </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52097,12 +53092,22 @@
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS282" t="inlineStr"/>
       <c r="AT282" t="n">
         <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
@@ -52223,6 +53228,11 @@
       <c r="R283" t="n">
         <v>0</v>
       </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52235,12 +53245,22 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
         <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
@@ -52361,6 +53381,11 @@
       <c r="R284" t="n">
         <v>0</v>
       </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52373,12 +53398,22 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr"/>
       <c r="AT284" t="n">
         <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
@@ -52499,6 +53534,11 @@
       <c r="R285" t="n">
         <v>0</v>
       </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52511,12 +53551,22 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
         <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
@@ -52637,6 +53687,11 @@
       <c r="R286" t="n">
         <v>0</v>
       </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52649,12 +53704,22 @@
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr"/>
       <c r="AT286" t="n">
         <v>0</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
@@ -52775,6 +53840,11 @@
       <c r="R287" t="n">
         <v>0</v>
       </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA287" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52787,12 +53857,22 @@
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr"/>
       <c r="AT287" t="n">
         <v>0</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
